--- a/nriss-patch-2/ig/StructureDefinition-fr-observation-pregnancy-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-observation-pregnancy-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -848,7 +848,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-observation-grossesse-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-observation-grossesse-cisis|20260916095452</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1125,7 +1125,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260916095455</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1214,7 +1214,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260916095453</t>
   </si>
   <si>
     <t>OBX-17</t>
